--- a/backend/data/financials_by_company/105630.KS.xlsx
+++ b/backend/data/financials_by_company/105630.KS.xlsx
@@ -4877,7 +4877,7 @@
         <v>82850398208</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
         <v>0.13152</v>
